--- a/Avance de Proyecto/PMOinformatica Plantilla de matriz de trazabilidad de requisitos.xls.xlsx
+++ b/Avance de Proyecto/PMOinformatica Plantilla de matriz de trazabilidad de requisitos.xls.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c84f6c42465ed23/Escritorio/MASTER/Universidad/9no Semestre/Comunicacion de Datos/ProyIntComDat25B_3.1416chul-s/ProyIntComDat25B_3.1416chul-s/Avance de Proyecto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6591D62-A935-45D6-9911-A6F8A66ACAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{E6591D62-A935-45D6-9911-A6F8A66ACAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0B471BC-8BE3-4485-A460-0CB82248AEB7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="175">
   <si>
     <t>Plantilla de matriz de trazabilidad de requisitos</t>
   </si>
@@ -102,31 +102,19 @@
     <t>Nivel de prioridad</t>
   </si>
   <si>
-    <t>Documentar proceso de inscripción en plataforma</t>
-  </si>
-  <si>
     <t>v1</t>
   </si>
   <si>
     <t>Aprobado</t>
   </si>
   <si>
-    <t>Guía PDF clara y entendible</t>
-  </si>
-  <si>
     <t>Moderada</t>
-  </si>
-  <si>
-    <t>Estudiantes no comprenden el proceso</t>
   </si>
   <si>
     <t>Recolectar y organizar info</t>
   </si>
   <si>
     <t>Guía PDF</t>
-  </si>
-  <si>
-    <t>Plantilla con capturas</t>
   </si>
   <si>
     <t>Captura y edición</t>
@@ -165,46 +153,10 @@
     <t>Encuesta de comprensión</t>
   </si>
   <si>
-    <t>Documentar entrega de tareas</t>
-  </si>
-  <si>
     <t>Solicitado</t>
   </si>
   <si>
     <t>Guía clara paso a paso</t>
-  </si>
-  <si>
-    <t>Disminuir errores de entrega</t>
-  </si>
-  <si>
-    <t>Plantilla uniforme</t>
-  </si>
-  <si>
-    <t>Redacción simple</t>
-  </si>
-  <si>
-    <t>Validación con piloto</t>
-  </si>
-  <si>
-    <t>Carlos Alberto Rojas Hernández (Encargado de Moodle)</t>
-  </si>
-  <si>
-    <t>Guía para recuperar contraseña</t>
-  </si>
-  <si>
-    <t>Guía PDF validada</t>
-  </si>
-  <si>
-    <t>Problema frecuente en alumnos</t>
-  </si>
-  <si>
-    <t>Plantilla gráfica</t>
-  </si>
-  <si>
-    <t>Capturas simples</t>
-  </si>
-  <si>
-    <t>Casos de prueba</t>
   </si>
   <si>
     <t>Equipo de desarrollo</t>
@@ -285,13 +237,7 @@
     <t xml:space="preserve">Equipo de desarrollo  </t>
   </si>
   <si>
-    <t>Grabar video de inscripción</t>
-  </si>
-  <si>
     <t>Video ≤3 min, funcional</t>
-  </si>
-  <si>
-    <t>Comprensión visual</t>
   </si>
   <si>
     <t>Elaborar videos</t>
@@ -300,19 +246,7 @@
     <t>Video editado</t>
   </si>
   <si>
-    <t>Plantilla de grabación</t>
-  </si>
-  <si>
-    <t>Software libre (OBS)</t>
-  </si>
-  <si>
-    <t>Grupo piloto</t>
-  </si>
-  <si>
     <t>Grabar video de calificaciones</t>
-  </si>
-  <si>
-    <t>Duración ≤2 min</t>
   </si>
   <si>
     <t>Apoyo al estudiante</t>
@@ -325,45 +259,6 @@
   </si>
   <si>
     <t>Retroalimentación usuarios</t>
-  </si>
-  <si>
-    <t>Grabar video de entrega de tareas</t>
-  </si>
-  <si>
-    <t>Claro y accesible</t>
-  </si>
-  <si>
-    <t>Evitar fallos en entregas</t>
-  </si>
-  <si>
-    <t>Capturas narradas</t>
-  </si>
-  <si>
-    <t>Edición sencilla</t>
-  </si>
-  <si>
-    <t>Encuesta de prueba</t>
-  </si>
-  <si>
-    <t>Subtítulos en videos</t>
-  </si>
-  <si>
-    <t>Subtítulos correctos</t>
-  </si>
-  <si>
-    <t>Inclusión y accesibilidad</t>
-  </si>
-  <si>
-    <t>Videos finales</t>
-  </si>
-  <si>
-    <t>Diseño accesible</t>
-  </si>
-  <si>
-    <t>Edición</t>
-  </si>
-  <si>
-    <t>Revisión accesibilidad</t>
   </si>
   <si>
     <t>Exportación de videos en MP4</t>
@@ -618,6 +513,60 @@
   <si>
     <t>Según la evaluación de la importancia del requisito para el logro de los objetivos del proyecto, se asigna un nivel de prioridad. Este nivel también puede depender del grado de influencia del interesado y estrategias que se estén empleando para gestionar la participación de los interesados.</t>
   </si>
+  <si>
+    <t>Tutorial y uso de la plataforma Microsoft Teams</t>
+  </si>
+  <si>
+    <t>Video/Guía PDF clara y entendible</t>
+  </si>
+  <si>
+    <t>Capacitar a estudiantes para clases virtuales.</t>
+  </si>
+  <si>
+    <t>Plantilla con capturas y pasos</t>
+  </si>
+  <si>
+    <t>Documentar como dar de baja una materia</t>
+  </si>
+  <si>
+    <t>Orientar a estudiantes en procesos administrativos</t>
+  </si>
+  <si>
+    <t>Validación con control escolar</t>
+  </si>
+  <si>
+    <t>Guía de registro de becas institucionales</t>
+  </si>
+  <si>
+    <t>Guía PDF con requisitos y pasos</t>
+  </si>
+  <si>
+    <t>Asegurar que más estudiantes accedan a becas</t>
+  </si>
+  <si>
+    <t>Plantilla con capturas y requisitos</t>
+  </si>
+  <si>
+    <t>María Candelaria Mónica Niembro Gaona(Encargarda de becas)</t>
+  </si>
+  <si>
+    <t>Grabar uso de la plataforma Microsoft Teams</t>
+  </si>
+  <si>
+    <t>Mejorar el dominio de Teams en estudiantes</t>
+  </si>
+  <si>
+    <t>Grabar video dar de baja una materia</t>
+  </si>
+  <si>
+    <t>Procesos administrativos digitales claros</t>
+  </si>
+  <si>
+    <t>Grabar el registro de becas institucionales</t>
+  </si>
+  <si>
+    <t>Explicar pasos para registro en línea</t>
+  </si>
 </sst>
 </file>
 
@@ -785,10 +734,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1223,46 +1168,46 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="E7" s="12" t="s">
         <v>21</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>22</v>
       </c>
       <c r="F7" s="15">
         <v>45930</v>
       </c>
       <c r="G7" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="K7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="L7" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="M7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="N7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="O7" s="8" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
@@ -1283,46 +1228,46 @@
         <v>1.2</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" s="15">
         <v>45930</v>
       </c>
       <c r="G8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="M8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="N8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="8" t="s">
+      <c r="O8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>31</v>
-      </c>
       <c r="P8" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
@@ -1343,46 +1288,46 @@
         <v>1.3</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F9" s="15">
         <v>45930</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>44</v>
+      <c r="L9" s="8" t="s">
+        <v>160</v>
       </c>
-      <c r="J9" s="8" t="s">
-        <v>37</v>
+      <c r="M9" s="8" t="s">
+        <v>35</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="N9" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="O9" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="O9" s="12" t="s">
-        <v>48</v>
-      </c>
       <c r="P9" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
@@ -1403,46 +1348,46 @@
         <v>1.4</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>49</v>
+        <v>164</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F10" s="15">
         <v>45930</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="H10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="M10" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>53</v>
-      </c>
       <c r="N10" s="12" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>55</v>
+        <v>168</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
@@ -1463,46 +1408,46 @@
         <v>2.1</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" s="15">
         <v>45930</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
@@ -1523,46 +1468,46 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F12" s="15">
         <v>45930</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
@@ -1583,46 +1528,46 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F13" s="15">
         <v>45930</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="J13" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="L13" s="8" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -1643,46 +1588,46 @@
         <v>3.1</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F14" s="15">
         <v>45931</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
@@ -1703,46 +1648,46 @@
         <v>3.2</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F15" s="15">
         <v>45931</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="O15" s="12" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -1763,46 +1708,46 @@
         <v>3.3</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>95</v>
+        <v>171</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F16" s="15">
         <v>45931</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
@@ -1823,46 +1768,46 @@
         <v>3.4</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F17" s="15">
         <v>45982</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="O17" s="12" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
@@ -1883,46 +1828,46 @@
         <v>3.5</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F18" s="15">
         <v>45984</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
@@ -1943,46 +1888,46 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F19" s="15">
         <v>45990</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P19" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
@@ -2003,46 +1948,46 @@
         <v>4.2</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F20" s="15">
         <v>45990</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
@@ -2063,46 +2008,46 @@
         <v>4.3</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F21" s="15">
         <v>45949</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
@@ -2123,46 +2068,46 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F22" s="15">
         <v>46003</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
@@ -2183,46 +2128,46 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F23" s="15">
         <v>46002</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
@@ -2243,46 +2188,46 @@
         <v>5.2</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F24" s="15">
         <v>46011</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
@@ -2303,46 +2248,46 @@
         <v>5.3</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F25" s="15">
         <v>45962</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
@@ -2363,46 +2308,46 @@
         <v>5.4</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F26" s="15">
         <v>46021</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
@@ -29797,7 +29742,7 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -29827,10 +29772,10 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -29863,7 +29808,7 @@
         <v>Identificación</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -29896,7 +29841,7 @@
         <v>Sub identificación</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -29929,7 +29874,7 @@
         <v>Descripción del requisito</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -29962,7 +29907,7 @@
         <v>Versión</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -29995,7 +29940,7 @@
         <v>Estado actual</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -30028,7 +29973,7 @@
         <v>Última fecha estado registrado</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -30061,7 +30006,7 @@
         <v>Criterios de aceptación</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -30094,7 +30039,7 @@
         <v>Nivel de complejidad</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -30127,7 +30072,7 @@
         <v>Necesidad, oportunidades u objetivos de negocio</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -30160,7 +30105,7 @@
         <v>Objetivo del proyecto</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -30193,7 +30138,7 @@
         <v>Entregables (EDT)</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -30226,7 +30171,7 @@
         <v>Diseño del producto</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -30259,7 +30204,7 @@
         <v>Desarrollo del producto</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -30292,7 +30237,7 @@
         <v>Estrategia y escenarios de pruebas</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -30325,7 +30270,7 @@
         <v>Interesado (Stakeholder) dueño del requisito</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -30358,7 +30303,7 @@
         <v>Nivel de prioridad</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -57804,12 +57749,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0fa9766c-9bcd-4ad8-8425-98b74b0d2252" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -58040,17 +57984,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0fa9766c-9bcd-4ad8-8425-98b74b0d2252" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12716809-A2C5-4BB3-BB0A-F0C3124F50CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E1DE7B6-29CE-4FAD-801A-1BB807154730}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="6af09f24-5ef0-42a5-957c-ff861d9f3bca"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="0fa9766c-9bcd-4ad8-8425-98b74b0d2252"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -58075,18 +58029,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E1DE7B6-29CE-4FAD-801A-1BB807154730}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12716809-A2C5-4BB3-BB0A-F0C3124F50CB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="6af09f24-5ef0-42a5-957c-ff861d9f3bca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="0fa9766c-9bcd-4ad8-8425-98b74b0d2252"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Avance de Proyecto/PMOinformatica Plantilla de matriz de trazabilidad de requisitos.xls.xlsx
+++ b/Avance de Proyecto/PMOinformatica Plantilla de matriz de trazabilidad de requisitos.xls.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c84f6c42465ed23/Escritorio/MASTER/Universidad/9no Semestre/Comunicacion de Datos/ProyIntComDat25B_3.1416chul-s/ProyIntComDat25B_3.1416chul-s/Avance de Proyecto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{E6591D62-A935-45D6-9911-A6F8A66ACAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0B471BC-8BE3-4485-A460-0CB82248AEB7}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{E6591D62-A935-45D6-9911-A6F8A66ACAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D765A1D-182A-48F4-B68B-AAFD4D01FCAB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8595" yWindow="0" windowWidth="12000" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plantilla de matriz requisitos" sheetId="1" r:id="rId1"/>
@@ -2257,7 +2257,7 @@
         <v>37</v>
       </c>
       <c r="F25" s="15">
-        <v>45962</v>
+        <v>46023</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>123</v>
@@ -2317,7 +2317,7 @@
         <v>37</v>
       </c>
       <c r="F26" s="15">
-        <v>46021</v>
+        <v>46052</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>132</v>

--- a/Avance de Proyecto/PMOinformatica Plantilla de matriz de trazabilidad de requisitos.xls.xlsx
+++ b/Avance de Proyecto/PMOinformatica Plantilla de matriz de trazabilidad de requisitos.xls.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c84f6c42465ed23/Escritorio/MASTER/Universidad/9no Semestre/Comunicacion de Datos/ProyIntComDat25B_3.1416chul-s/ProyIntComDat25B_3.1416chul-s/Avance de Proyecto/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lmeji\Desktop\MASTER\Universidad\9no Semestre\Comunicacion de Datos\ProyIntComDat25B_3.1416chul-s\ProyIntComDat25B_3.1416chul-s\Avance de Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{E6591D62-A935-45D6-9911-A6F8A66ACAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D765A1D-182A-48F4-B68B-AAFD4D01FCAB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB930B3E-2DFD-45D3-845B-E8324E28810E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8595" yWindow="0" windowWidth="12000" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plantilla de matriz requisitos" sheetId="1" r:id="rId1"/>
@@ -1177,7 +1177,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="15">
-        <v>45930</v>
+        <v>45944</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>158</v>
@@ -1237,7 +1237,7 @@
         <v>21</v>
       </c>
       <c r="F8" s="15">
-        <v>45930</v>
+        <v>45944</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>30</v>
@@ -1297,7 +1297,7 @@
         <v>37</v>
       </c>
       <c r="F9" s="15">
-        <v>45930</v>
+        <v>45944</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>38</v>
@@ -1357,7 +1357,7 @@
         <v>37</v>
       </c>
       <c r="F10" s="15">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>165</v>
@@ -1417,7 +1417,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="15">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>42</v>
@@ -1477,7 +1477,7 @@
         <v>37</v>
       </c>
       <c r="F12" s="15">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>50</v>
@@ -1537,7 +1537,7 @@
         <v>37</v>
       </c>
       <c r="F13" s="15">
-        <v>45930</v>
+        <v>45944</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>58</v>
@@ -1597,7 +1597,7 @@
         <v>37</v>
       </c>
       <c r="F14" s="15">
-        <v>45931</v>
+        <v>45955</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>65</v>
@@ -1657,7 +1657,7 @@
         <v>37</v>
       </c>
       <c r="F15" s="15">
-        <v>45931</v>
+        <v>45955</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>65</v>
@@ -1717,7 +1717,7 @@
         <v>37</v>
       </c>
       <c r="F16" s="15">
-        <v>45931</v>
+        <v>45957</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>65</v>
@@ -1777,7 +1777,7 @@
         <v>37</v>
       </c>
       <c r="F17" s="15">
-        <v>45982</v>
+        <v>45961</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>65</v>
@@ -1837,7 +1837,7 @@
         <v>37</v>
       </c>
       <c r="F18" s="15">
-        <v>45984</v>
+        <v>45962</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>74</v>
@@ -1897,7 +1897,7 @@
         <v>37</v>
       </c>
       <c r="F19" s="15">
-        <v>45990</v>
+        <v>45966</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>81</v>
@@ -1957,7 +1957,7 @@
         <v>37</v>
       </c>
       <c r="F20" s="15">
-        <v>45990</v>
+        <v>45968</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>89</v>
@@ -2017,7 +2017,7 @@
         <v>37</v>
       </c>
       <c r="F21" s="15">
-        <v>45949</v>
+        <v>45971</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>94</v>
@@ -2077,7 +2077,7 @@
         <v>37</v>
       </c>
       <c r="F22" s="15">
-        <v>46003</v>
+        <v>45976</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>101</v>
@@ -2137,7 +2137,7 @@
         <v>37</v>
       </c>
       <c r="F23" s="15">
-        <v>46002</v>
+        <v>45981</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>107</v>
@@ -2197,7 +2197,7 @@
         <v>37</v>
       </c>
       <c r="F24" s="15">
-        <v>46011</v>
+        <v>45989</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>114</v>
@@ -2257,7 +2257,7 @@
         <v>37</v>
       </c>
       <c r="F25" s="15">
-        <v>46023</v>
+        <v>45994</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>123</v>
@@ -2317,7 +2317,7 @@
         <v>37</v>
       </c>
       <c r="F26" s="15">
-        <v>46052</v>
+        <v>45996</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>132</v>
@@ -57757,6 +57757,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004C1A3113D649624F9135CDBD3D69C302" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="13ffc8dcfefe0bebfe1d287b721fe34d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6af09f24-5ef0-42a5-957c-ff861d9f3bca" xmlns:ns4="0fa9766c-9bcd-4ad8-8425-98b74b0d2252" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="df4ecb7d677b47b7113d60f963805797" ns3:_="" ns4:_="">
     <xsd:import namespace="6af09f24-5ef0-42a5-957c-ff861d9f3bca"/>
@@ -57983,15 +57992,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E1DE7B6-29CE-4FAD-801A-1BB807154730}">
   <ds:schemaRefs>
@@ -58010,6 +58010,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12716809-A2C5-4BB3-BB0A-F0C3124F50CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EED8B2CD-5E4B-4E79-A91C-8550F2629E73}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -58026,12 +58034,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12716809-A2C5-4BB3-BB0A-F0C3124F50CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>